--- a/word.xlsx
+++ b/word.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10965" windowHeight="9712"/>
+    <workbookView windowWidth="11355" windowHeight="9150"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>单词</t>
   </si>
@@ -80,6 +80,12 @@
   </si>
   <si>
     <t>有（无人称）；助动词</t>
+  </si>
+  <si>
+    <t>casa</t>
+  </si>
+  <si>
+    <t>房子</t>
   </si>
 </sst>
 </file>
@@ -1018,8 +1024,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
@@ -1111,6 +1117,17 @@
       </c>
       <c r="C7" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
